--- a/examples/diccionario_codigos_tesistas.xlsx
+++ b/examples/diccionario_codigos_tesistas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">category</t>
   </si>
@@ -26,172 +26,46 @@
     <t xml:space="preserve">Factores personales</t>
   </si>
   <si>
-    <t xml:space="preserve">motivacion_intrinseca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razones internas, pasion o intereses personales del tesista que lo impulsan a realizar la tesis (ej: tema que le duele, vocacion, conviccion etica).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autoeficacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creencia del tesista sobre su propia capacidad para completar la tesis; confianza o inseguridad frente a los retos academicos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">autoexigencia_perfeccionismo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exigencia interna desproporcionada, estandares perfeccionistas que bloquean el avance o generan insatisfaccion con el propio trabajo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gestion_del_tiempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descripciones sobre como el tesista organiza, planifica o falla en administrar el tiempo disponible para la tesis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">salud_mental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menciones de ansiedad, depresion, burnout, insomnio, atencion psicologica o psiquiatrica, trastornos o sintomas mentales atribuidos al proceso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estrategias_afrontamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tacticas, rutinas o estrategias concretas que el tesista aplica para manejar dificultades (ej: Pomodoro, escribir mal, dividir tareas).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">procrastinacion_evitacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conductas de postergacion, evitacion del trabajo, uso de distractores (Netflix, redes) para no enfrentar la tesis.</t>
+    <t xml:space="preserve">Motivacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razones internas, pasion, vocacion o intereses personales del tesista que lo impulsan a realizar la investigacion. Incluye expresiones sobre que le apasiona el tema, se identifica con el problema, quiere aportar a su campo, o tiene una motivacion etica. Ejemplo: 'elegi este tema porque me duele, tengo familia en zonas rurales sin agua'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripciones sobre como el tesista administra, planifica, pierde o sacrifica el tiempo para avanzar la tesis. Incluye: jornadas dobles, trabajo nocturno, falta de horas, carga horaria, sacrificios de ocio/gimnasio/amigos, percepcion de plazos apretados, cansancio por exceso de horas dedicadas. Ejemplo: 'la tesis la hago de noche y los domingos', 'he vivido a punta de cafe este ultimo anio'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obstaculos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menciones de obstaculos, barreras o dificultades concretas en el proceso: bloqueos de escritura, salud mental afectada, problemas tecnicos (grabadora, laptop), crisis de abandono, procrastinacion, parálisis por perfeccionismo, comparacion con otros, falta de autoeficacia, problemas de muestreo, rechazo institucional. Ejemplo: 'estoy paralizada, cada vez que abro Word borro lo que escribo', 'la empresa me cancelo el convenio'.</t>
   </si>
   <si>
     <t xml:space="preserve">Factores institucionales</t>
   </si>
   <si>
-    <t xml:space="preserve">asesor_distante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descripciones del asesor como poco disponible, con respuestas tardias, falta de feedback sustantivo o ausencia de seguimiento.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asesor_exigente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asesor descrito como duro, demandante, con altas expectativas y retroalimentacion critica pero comprometido con la formacion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asesor_sobreinvolucrado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asesor con presencia excesiva, intrusiva, demandas fuera de horario, vigilancia constante del avance o perdida de autonomia del tesista.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metodologia_investigacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Referencias a aspectos metodologicos de la investigacion: diseno, muestreo, instrumentos, analisis de datos, validez, rigor cientifico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">burocracia_universitaria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramites, requisitos, reglamentos, plazos institucionales que generan friccion o retrasos al proceso de tesis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recursos_universidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Servicios de la universidad que el tesista uso o valoro (biblioteca, psicologia universitaria, talleres, asesorias metodologicas, plataformas).</t>
+    <t xml:space="preserve">Metodologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias a aspectos metodologicos de la investigacion: diseno de estudio, muestreo, instrumentos, analisis de datos (SPSS, software cuantitativo o cualitativo), validez, codificacion, entrevistas, grupos focales, saturacion teorica, triangulacion, calidad del rigor cientifico. Ejemplo: 'estoy en analisis de datos, apliqué un instrumento a 312 universitarios', 'mi tesis es cualitativa, llevo 7 entrevistas'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asesor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripciones sobre la figura y rol del asesor/a: disponibilidad, estilo de supervision, feedback, exigencia, relacion de trabajo, conflictos o satisfaccion con el acompanamiento. Incluye asesor distante, exigente, sobreinvolucrado, comprometido, ausente, critico o paciente. Ejemplo: 'el doctor Mendoza es duro pero me esta formando', 'mi asesora me llama los domingos a las 8 de la manana'.</t>
   </si>
   <si>
     <t xml:space="preserve">Factores sociales</t>
   </si>
   <si>
-    <t xml:space="preserve">apoyo_familiar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Soporte emocional, consejos o ayuda practica de familiares (padres, hermanos) durante el proceso de tesis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apoyo_pareja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apoyo, paciencia o tension con la pareja/conyugue derivada de la dedicacion a la tesis (incluidas rupturas por la tesis).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">grupo_pares_tesistas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relaciones con otros tesistas (grupos de estudio, WhatsApp, amistades academicas) que sirven como soporte emocional o tecnico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comparacion_social</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Menciones donde el tesista se compara con companeros (ritmo, logros, publicaciones) generando ansiedad, envidia o sensacion de retraso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aislamiento_academico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percepcion de soledad durante el proceso, falta de red de apoyo, encierro social, sensacion de estar solo frente al trabajo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Factores economicos y laborales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trabajo_paralelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compatibilizacion entre trabajo remunerado y tesis, incluyendo cansancio, jornada doble, horarios restringidos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sacrificio_economico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gastos asociados a la tesis (estadistico, impresiones, conferencias, datos) y el esfuerzo economico que implican.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">necesidad_financiamiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Necesidad de financiamiento, becas, apoyo economico para poder continuar; preocupaciones economicas del tesista.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experiencias emocionales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crisis_abandono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Momentos concretos en que el tesista penso en abandonar, considero retirar la tesis, tuvo crisis de desmotivacion aguda o quiso rendirse.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">logro_avance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Satisfaccion por avances concretos: capitulo terminado, aprobacion del tribunal, defensa exitosa, reconocimiento del asesor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">proceso_transformador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reflexiones sobre como el proceso cambio al tesista: aprendizajes personales, cambio de perspectiva, habilidades nuevas, madurez.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emocion_negativa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expresiones de tristeza, frustracion, rabia, impotencia, miedo, culpa, agotamiento vinculadas al proceso de tesis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emocion_positiva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expresiones de alegria, orgullo, esperanza, gratitud, alivio asociadas con momentos o personas durante la tesis.</t>
+    <t xml:space="preserve">Apoyo emocional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soporte emocional, consejos o ayuda practica recibidos de red social cercana: familia (padres, hermanos), pareja/conyuge, companeros tesistas, amigos, grupos de WhatsApp, psicologos o psiquiatras. Tambien incluye sensacion de aislamiento academico o soledad por falta de esta red. Ejemplo: 'mi papa me dijo no abandones', 'un grupo de Facebook de tesistas con TDAH me cambio la perspectiva'.</t>
   </si>
 </sst>
 </file>
@@ -219,7 +93,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,16 +120,6 @@
         <fgColor rgb="FFE8F8F0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEF5E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF2F8"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -274,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -286,12 +150,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -584,9 +442,9 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="32.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="32.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="90.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="28.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="110.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,256 +492,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/examples/diccionario_codigos_tesistas.xlsx
+++ b/examples/diccionario_codigos_tesistas.xlsx
@@ -14,13 +14,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
-    <t xml:space="preserve">category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code</t>
-  </si>
-  <si>
-    <t xml:space="preserve">definition</t>
+    <t xml:space="preserve">Categoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Definición</t>
   </si>
   <si>
     <t xml:space="preserve">Factores personales</t>
